--- a/高波精选组.xlsx
+++ b/高波精选组.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\GopherHK\Fixed Income\结构化产品\HTML 生成\FCN_Watchlist_交接\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8DA89F-E88D-4E62-A704-665B1F9A2119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8118352-6F1E-4EDD-B6D4-3B5CEFB63DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="68">
   <si>
     <t>区域</t>
   </si>
@@ -73,10 +73,22 @@
     <t>Copper</t>
   </si>
   <si>
-    <t>358 HK</t>
-  </si>
-  <si>
-    <t>江西铜业股份</t>
+    <t>3993 HK</t>
+  </si>
+  <si>
+    <t>洛阳钼业</t>
+  </si>
+  <si>
+    <t>Other Industrial Metals &amp; Mining</t>
+  </si>
+  <si>
+    <t>522 HK</t>
+  </si>
+  <si>
+    <t>ASMPT</t>
+  </si>
+  <si>
+    <t>Semiconductor Equipment &amp; Materials</t>
   </si>
   <si>
     <t>1347 HK</t>
@@ -97,15 +109,6 @@
     <t>AI光通信</t>
   </si>
   <si>
-    <t>522 HK</t>
-  </si>
-  <si>
-    <t>ASMPT</t>
-  </si>
-  <si>
-    <t>Semiconductor Equipment &amp; Materials</t>
-  </si>
-  <si>
     <t>美股</t>
   </si>
   <si>
@@ -118,21 +121,33 @@
     <t>AI互联</t>
   </si>
   <si>
+    <t>TER US</t>
+  </si>
+  <si>
+    <t>泰瑞达</t>
+  </si>
+  <si>
+    <t>STX US</t>
+  </si>
+  <si>
+    <t>希捷科技</t>
+  </si>
+  <si>
+    <t>MU US</t>
+  </si>
+  <si>
+    <t>美光</t>
+  </si>
+  <si>
+    <t>内存/HBM</t>
+  </si>
+  <si>
     <t>ALAB US</t>
   </si>
   <si>
     <t>Astera Labs</t>
   </si>
   <si>
-    <t>MU US</t>
-  </si>
-  <si>
-    <t>美光</t>
-  </si>
-  <si>
-    <t>内存/HBM</t>
-  </si>
-  <si>
     <t>DELL US</t>
   </si>
   <si>
@@ -148,6 +163,15 @@
     <t>Communication Equipment</t>
   </si>
   <si>
+    <t>AMD US</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>AI芯片</t>
+  </si>
+  <si>
     <t>ANET US</t>
   </si>
   <si>
@@ -157,37 +181,31 @@
     <t>AI网络</t>
   </si>
   <si>
-    <t>MRVL US</t>
-  </si>
-  <si>
-    <t>Marvell</t>
-  </si>
-  <si>
-    <t>客制硅/互联</t>
-  </si>
-  <si>
-    <t>TER US</t>
-  </si>
-  <si>
-    <t>泰瑞达</t>
-  </si>
-  <si>
-    <t>AMAT US</t>
-  </si>
-  <si>
-    <t>应用材料</t>
-  </si>
-  <si>
-    <t>STX US</t>
-  </si>
-  <si>
-    <t>希捷科技</t>
-  </si>
-  <si>
-    <t>LITE US</t>
-  </si>
-  <si>
-    <t>Lumentum</t>
+    <t>DDOG US</t>
+  </si>
+  <si>
+    <t>Datadog</t>
+  </si>
+  <si>
+    <t>Software - Application</t>
+  </si>
+  <si>
+    <t>RDDT US</t>
+  </si>
+  <si>
+    <t>Reddit</t>
+  </si>
+  <si>
+    <t>Internet Content &amp; Information</t>
+  </si>
+  <si>
+    <t>CVNA US</t>
+  </si>
+  <si>
+    <t>Carvana</t>
+  </si>
+  <si>
+    <t>Auto &amp; Truck Dealerships</t>
   </si>
   <si>
     <t>CCL US</t>
@@ -199,22 +217,13 @@
     <t>Travel Services</t>
   </si>
   <si>
-    <t>CVNA US</t>
-  </si>
-  <si>
-    <t>Carvana</t>
-  </si>
-  <si>
-    <t>Auto &amp; Truck Dealerships</t>
-  </si>
-  <si>
-    <t>GEV US</t>
-  </si>
-  <si>
-    <t>GE Vernova</t>
-  </si>
-  <si>
-    <t>Specialty Industrial Machinery</t>
+    <t>VRT US</t>
+  </si>
+  <si>
+    <t>Vertiv</t>
+  </si>
+  <si>
+    <t>数据中心冷却</t>
   </si>
 </sst>
 </file>
@@ -608,10 +617,10 @@
         <v>12</v>
       </c>
       <c r="E2">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="F2">
-        <v>0.62</v>
+        <v>0.7</v>
       </c>
       <c r="G2" t="s">
         <v>13</v>
@@ -620,7 +629,7 @@
         <v>1.01</v>
       </c>
       <c r="I2" s="1">
-        <v>0.19320000000000001</v>
+        <v>0.20150000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.15">
@@ -649,7 +658,7 @@
         <v>1.01</v>
       </c>
       <c r="I3" s="1">
-        <v>0.18940000000000001</v>
+        <v>0.11310000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.15">
@@ -663,13 +672,13 @@
         <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E4">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="F4">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="G4" t="s">
         <v>13</v>
@@ -678,7 +687,7 @@
         <v>1.01</v>
       </c>
       <c r="I4" s="1">
-        <v>0.18010000000000001</v>
+        <v>0.19980000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.15">
@@ -686,19 +695,19 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="F5">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="G5" t="s">
         <v>13</v>
@@ -707,7 +716,7 @@
         <v>1.01</v>
       </c>
       <c r="I5" s="1">
-        <v>0.24829999999999999</v>
+        <v>0.22170000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.15">
@@ -715,19 +724,19 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6">
-        <v>0.5</v>
+        <v>0.77</v>
       </c>
       <c r="F6">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -736,7 +745,7 @@
         <v>1.01</v>
       </c>
       <c r="I6" s="1">
-        <v>5.04E-2</v>
+        <v>0.26500000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.15">
@@ -744,19 +753,19 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E7">
-        <v>0.74</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="F7">
-        <v>0.64</v>
+        <v>0.46</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -765,27 +774,27 @@
         <v>1.01</v>
       </c>
       <c r="I7" s="1">
-        <v>0.2135</v>
+        <v>8.9099999999999999E-2</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E8">
-        <v>0.57999999999999996</v>
+        <v>0.62</v>
       </c>
       <c r="F8">
-        <v>0.48</v>
+        <v>0.52</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -794,27 +803,27 @@
         <v>1.01</v>
       </c>
       <c r="I8" s="1">
-        <v>0.27129999999999999</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E9">
-        <v>0.56000000000000005</v>
+        <v>0.71</v>
       </c>
       <c r="F9">
-        <v>0.46</v>
+        <v>0.61</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -823,27 +832,27 @@
         <v>1.01</v>
       </c>
       <c r="I9" s="1">
-        <v>0.24340000000000001</v>
+        <v>0.25569999999999998</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="E10">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="F10">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -852,12 +861,12 @@
         <v>1.01</v>
       </c>
       <c r="I10" s="1">
-        <v>0.26979999999999998</v>
+        <v>0.27800000000000002</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11" t="s">
         <v>37</v>
@@ -866,13 +875,13 @@
         <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E11">
-        <v>0.69</v>
+        <v>0.7</v>
       </c>
       <c r="F11">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
@@ -881,27 +890,27 @@
         <v>1.01</v>
       </c>
       <c r="I11" s="1">
-        <v>0.28070000000000001</v>
+        <v>0.20699999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="E12">
-        <v>0.74</v>
+        <v>0.64</v>
       </c>
       <c r="F12">
-        <v>0.64</v>
+        <v>0.54</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
@@ -910,12 +919,12 @@
         <v>1.01</v>
       </c>
       <c r="I12" s="1">
-        <v>0.25990000000000002</v>
+        <v>0.2641</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B13" t="s">
         <v>42</v>
@@ -924,13 +933,13 @@
         <v>43</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="E13">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="F13">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
@@ -939,27 +948,27 @@
         <v>1.01</v>
       </c>
       <c r="I13" s="1">
-        <v>0.19270000000000001</v>
+        <v>0.29820000000000002</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" t="s">
         <v>45</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>46</v>
       </c>
-      <c r="D14" t="s">
-        <v>47</v>
-      </c>
       <c r="E14">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="F14">
-        <v>0.57999999999999996</v>
+        <v>0.6</v>
       </c>
       <c r="G14" t="s">
         <v>13</v>
@@ -968,28 +977,28 @@
         <v>1.01</v>
       </c>
       <c r="I14" s="1">
-        <v>0.2757</v>
+        <v>0.19439999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" t="s">
         <v>48</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>49</v>
       </c>
-      <c r="D15" t="s">
-        <v>27</v>
-      </c>
       <c r="E15">
+        <v>0.77</v>
+      </c>
+      <c r="F15">
         <v>0.67</v>
       </c>
-      <c r="F15">
-        <v>0.56999999999999995</v>
-      </c>
       <c r="G15" t="s">
         <v>13</v>
       </c>
@@ -997,12 +1006,12 @@
         <v>1.01</v>
       </c>
       <c r="I15" s="1">
-        <v>0.27160000000000001</v>
+        <v>0.1918</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
         <v>50</v>
@@ -1011,13 +1020,13 @@
         <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="E16">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="F16">
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
@@ -1026,27 +1035,27 @@
         <v>1.01</v>
       </c>
       <c r="I16" s="1">
-        <v>0.2772</v>
+        <v>0.219</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D17" t="s">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="E17">
-        <v>0.68</v>
+        <v>0.77</v>
       </c>
       <c r="F17">
-        <v>0.57999999999999996</v>
+        <v>0.67</v>
       </c>
       <c r="G17" t="s">
         <v>13</v>
@@ -1055,27 +1064,27 @@
         <v>1.01</v>
       </c>
       <c r="I17" s="1">
-        <v>0.2923</v>
+        <v>0.1966</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D18" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="E18">
-        <v>0.6</v>
+        <v>0.74</v>
       </c>
       <c r="F18">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="G18" t="s">
         <v>13</v>
@@ -1084,27 +1093,27 @@
         <v>1.01</v>
       </c>
       <c r="I18" s="1">
-        <v>0.28189999999999998</v>
+        <v>0.21060000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D19" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E19">
-        <v>0.81</v>
+        <v>0.76</v>
       </c>
       <c r="F19">
-        <v>0.71</v>
+        <v>0.66</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
@@ -1113,28 +1122,28 @@
         <v>1.01</v>
       </c>
       <c r="I19" s="1">
-        <v>0.1384</v>
+        <v>0.1968</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C20" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D20" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E20">
+        <v>0.83</v>
+      </c>
+      <c r="F20">
         <v>0.73</v>
       </c>
-      <c r="F20">
-        <v>0.63</v>
-      </c>
       <c r="G20" t="s">
         <v>13</v>
       </c>
@@ -1142,27 +1151,27 @@
         <v>1.01</v>
       </c>
       <c r="I20" s="1">
-        <v>0.19620000000000001</v>
+        <v>0.1426</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B21" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C21" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D21" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E21">
-        <v>0.81</v>
+        <v>0.75</v>
       </c>
       <c r="F21">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="G21" t="s">
         <v>13</v>
@@ -1171,7 +1180,7 @@
         <v>1.01</v>
       </c>
       <c r="I21" s="1">
-        <v>0.19339999999999999</v>
+        <v>0.20880000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/高波精选组.xlsx
+++ b/高波精选组.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\GopherHK\Fixed Income\结构化产品\HTML 生成\FCN_Watchlist_交接\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBEDDE70-C395-4FB6-B742-3834710912B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEE70054-EC34-4A10-BBDC-05E8301DB636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="66">
   <si>
     <t>区域</t>
   </si>
@@ -65,6 +65,27 @@
     <t>港股</t>
   </si>
   <si>
+    <t>992 HK</t>
+  </si>
+  <si>
+    <t>联想集团</t>
+  </si>
+  <si>
+    <t>计算机硬件</t>
+  </si>
+  <si>
+    <t>欧式敲入</t>
+  </si>
+  <si>
+    <t>1208 HK</t>
+  </si>
+  <si>
+    <t>五矿资源</t>
+  </si>
+  <si>
+    <t>铜业</t>
+  </si>
+  <si>
     <t>1138 HK</t>
   </si>
   <si>
@@ -74,27 +95,6 @@
     <t>油气中游</t>
   </si>
   <si>
-    <t>欧式敲入</t>
-  </si>
-  <si>
-    <t>992 HK</t>
-  </si>
-  <si>
-    <t>联想集团</t>
-  </si>
-  <si>
-    <t>计算机硬件</t>
-  </si>
-  <si>
-    <t>1208 HK</t>
-  </si>
-  <si>
-    <t>五矿资源</t>
-  </si>
-  <si>
-    <t>铜业</t>
-  </si>
-  <si>
     <t>6869 HK</t>
   </si>
   <si>
@@ -104,6 +104,15 @@
     <t>AI光通信</t>
   </si>
   <si>
+    <t>1888 HK</t>
+  </si>
+  <si>
+    <t>建滔积层板</t>
+  </si>
+  <si>
+    <t>电子元件</t>
+  </si>
+  <si>
     <t>522 HK</t>
   </si>
   <si>
@@ -113,15 +122,6 @@
     <t>半导体设备与材料</t>
   </si>
   <si>
-    <t>981 HK</t>
-  </si>
-  <si>
-    <t>中芯国际</t>
-  </si>
-  <si>
-    <t>晶圆代工</t>
-  </si>
-  <si>
     <t>美股</t>
   </si>
   <si>
@@ -158,6 +158,12 @@
     <t>内存/HBM</t>
   </si>
   <si>
+    <t>STX US</t>
+  </si>
+  <si>
+    <t>希捷科技</t>
+  </si>
+  <si>
     <t>NET US</t>
   </si>
   <si>
@@ -182,10 +188,31 @@
     <t>泰瑞达</t>
   </si>
   <si>
-    <t>STX US</t>
-  </si>
-  <si>
-    <t>希捷科技</t>
+    <t>LITE US</t>
+  </si>
+  <si>
+    <t>Lumentum</t>
+  </si>
+  <si>
+    <t>PANW US</t>
+  </si>
+  <si>
+    <t>Palo Alto Networks</t>
+  </si>
+  <si>
+    <t>NOW US</t>
+  </si>
+  <si>
+    <t>ServiceNow</t>
+  </si>
+  <si>
+    <t>AMD US</t>
+  </si>
+  <si>
+    <t>超微半导体</t>
+  </si>
+  <si>
+    <t>AI芯片</t>
   </si>
   <si>
     <t>FIX US</t>
@@ -195,39 +222,6 @@
   </si>
   <si>
     <t>工程与建筑</t>
-  </si>
-  <si>
-    <t>NOW US</t>
-  </si>
-  <si>
-    <t>ServiceNow</t>
-  </si>
-  <si>
-    <t>AMD US</t>
-  </si>
-  <si>
-    <t>超微半导体</t>
-  </si>
-  <si>
-    <t>AI芯片</t>
-  </si>
-  <si>
-    <t>ALAB US</t>
-  </si>
-  <si>
-    <t>阿斯特拉实验室</t>
-  </si>
-  <si>
-    <t>半导体</t>
-  </si>
-  <si>
-    <t>MRVL US</t>
-  </si>
-  <si>
-    <t>迈威尔科技</t>
-  </si>
-  <si>
-    <t>客制硅/互联</t>
   </si>
   <si>
     <t>CVNA US</t>
@@ -584,10 +578,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -616,7 +610,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -630,10 +624,10 @@
         <v>12</v>
       </c>
       <c r="E2">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="F2">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="G2" t="s">
         <v>13</v>
@@ -642,18 +636,18 @@
         <v>1.01</v>
       </c>
       <c r="I2" s="1">
-        <v>0.17510000000000001</v>
+        <v>0.2024</v>
+      </c>
+      <c r="K2">
+        <f>E2*100</f>
+        <v>78</v>
       </c>
       <c r="L2">
-        <f>E2*100</f>
-        <v>76</v>
-      </c>
-      <c r="M2">
         <f>F2*100</f>
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.15">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -667,10 +661,10 @@
         <v>16</v>
       </c>
       <c r="E3">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="F3">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
@@ -679,18 +673,18 @@
         <v>1.01</v>
       </c>
       <c r="I3" s="1">
-        <v>0.19209999999999999</v>
+        <v>0.11890000000000001</v>
+      </c>
+      <c r="K3">
+        <f>E3*100</f>
+        <v>75</v>
       </c>
       <c r="L3">
-        <f>E3*100</f>
-        <v>80</v>
-      </c>
-      <c r="M3">
         <f>F3*100</f>
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -704,10 +698,10 @@
         <v>19</v>
       </c>
       <c r="E4">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="F4">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="G4" t="s">
         <v>13</v>
@@ -716,18 +710,18 @@
         <v>1.01</v>
       </c>
       <c r="I4" s="1">
-        <v>0.1116</v>
+        <v>0.16819999999999999</v>
+      </c>
+      <c r="K4">
+        <f>E4*100</f>
+        <v>76</v>
       </c>
       <c r="L4">
-        <f>E4*100</f>
-        <v>74</v>
-      </c>
-      <c r="M4">
         <f>F4*100</f>
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -741,10 +735,10 @@
         <v>22</v>
       </c>
       <c r="E5">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="F5">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="G5" t="s">
         <v>13</v>
@@ -753,18 +747,18 @@
         <v>1.01</v>
       </c>
       <c r="I5" s="1">
-        <v>0.23799999999999999</v>
+        <v>0.25380000000000003</v>
+      </c>
+      <c r="K5">
+        <f>E5*100</f>
+        <v>61</v>
       </c>
       <c r="L5">
-        <f>E5*100</f>
-        <v>59</v>
-      </c>
-      <c r="M5">
         <f>F5*100</f>
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.15">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -778,10 +772,10 @@
         <v>25</v>
       </c>
       <c r="E6">
-        <v>0.74</v>
+        <v>0.5</v>
       </c>
       <c r="F6">
-        <v>0.64</v>
+        <v>0.4</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -790,18 +784,18 @@
         <v>1.01</v>
       </c>
       <c r="I6" s="1">
-        <v>0.16700000000000001</v>
+        <v>9.3700000000000006E-2</v>
+      </c>
+      <c r="K6">
+        <f>E6*100</f>
+        <v>50</v>
       </c>
       <c r="L6">
-        <f>E6*100</f>
-        <v>74</v>
-      </c>
-      <c r="M6">
         <f>F6*100</f>
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.15">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -815,10 +809,10 @@
         <v>28</v>
       </c>
       <c r="E7">
-        <v>0.85</v>
+        <v>0.73</v>
       </c>
       <c r="F7">
-        <v>0.75</v>
+        <v>0.63</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -827,18 +821,18 @@
         <v>1.01</v>
       </c>
       <c r="I7" s="1">
-        <v>0.11459999999999999</v>
+        <v>0.1605</v>
+      </c>
+      <c r="K7">
+        <f>E7*100</f>
+        <v>73</v>
       </c>
       <c r="L7">
-        <f>E7*100</f>
-        <v>85</v>
-      </c>
-      <c r="M7">
         <f>F7*100</f>
-        <v>75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.15">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -849,13 +843,13 @@
         <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E8">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="F8">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -864,18 +858,18 @@
         <v>1.01</v>
       </c>
       <c r="I8" s="1">
-        <v>0.19259999999999999</v>
+        <v>0.19059999999999999</v>
+      </c>
+      <c r="K8">
+        <f>E8*100</f>
+        <v>72</v>
       </c>
       <c r="L8">
-        <f>E8*100</f>
-        <v>71</v>
-      </c>
-      <c r="M8">
         <f>F8*100</f>
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.15">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -889,10 +883,10 @@
         <v>34</v>
       </c>
       <c r="E9">
-        <v>0.81</v>
+        <v>0.8</v>
       </c>
       <c r="F9">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -901,18 +895,18 @@
         <v>1.01</v>
       </c>
       <c r="I9" s="1">
-        <v>0.19739999999999999</v>
+        <v>0.19980000000000001</v>
+      </c>
+      <c r="K9">
+        <f>E9*100</f>
+        <v>80</v>
       </c>
       <c r="L9">
-        <f>E9*100</f>
-        <v>81</v>
-      </c>
-      <c r="M9">
         <f>F9*100</f>
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.15">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -926,10 +920,10 @@
         <v>37</v>
       </c>
       <c r="E10">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="F10">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -938,18 +932,18 @@
         <v>1.01</v>
       </c>
       <c r="I10" s="1">
-        <v>0.18210000000000001</v>
+        <v>0.1734</v>
+      </c>
+      <c r="K10">
+        <f>E10*100</f>
+        <v>73</v>
       </c>
       <c r="L10">
-        <f>E10*100</f>
-        <v>75</v>
-      </c>
-      <c r="M10">
         <f>F10*100</f>
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.15">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -963,10 +957,10 @@
         <v>40</v>
       </c>
       <c r="E11">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="F11">
-        <v>0.67</v>
+        <v>0.69</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
@@ -975,18 +969,18 @@
         <v>1.01</v>
       </c>
       <c r="I11" s="1">
-        <v>0.18390000000000001</v>
+        <v>0.18279999999999999</v>
+      </c>
+      <c r="K11">
+        <f>E11*100</f>
+        <v>79</v>
       </c>
       <c r="L11">
-        <f>E11*100</f>
-        <v>77</v>
-      </c>
-      <c r="M11">
         <f>F11*100</f>
-        <v>67</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.15">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -997,13 +991,13 @@
         <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="E12">
-        <v>0.76</v>
+        <v>0.71</v>
       </c>
       <c r="F12">
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
@@ -1012,35 +1006,35 @@
         <v>1.01</v>
       </c>
       <c r="I12" s="1">
-        <v>0.19239999999999999</v>
+        <v>0.1993</v>
+      </c>
+      <c r="K12">
+        <f>E12*100</f>
+        <v>71</v>
       </c>
       <c r="L12">
-        <f>E12*100</f>
-        <v>76</v>
-      </c>
-      <c r="M12">
         <f>F12*100</f>
-        <v>66</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.15">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>29</v>
       </c>
       <c r="B13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" t="s">
         <v>44</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>45</v>
       </c>
-      <c r="D13" t="s">
-        <v>46</v>
-      </c>
       <c r="E13">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="F13">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
@@ -1049,35 +1043,35 @@
         <v>1.01</v>
       </c>
       <c r="I13" s="1">
-        <v>0.2019</v>
+        <v>0.20080000000000001</v>
+      </c>
+      <c r="K13">
+        <f>E13*100</f>
+        <v>76</v>
       </c>
       <c r="L13">
-        <f>E13*100</f>
-        <v>75</v>
-      </c>
-      <c r="M13">
         <f>F13*100</f>
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.15">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>29</v>
       </c>
       <c r="B14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" t="s">
         <v>47</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>48</v>
       </c>
-      <c r="D14" t="s">
-        <v>25</v>
-      </c>
       <c r="E14">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="F14">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="G14" t="s">
         <v>13</v>
@@ -1086,18 +1080,18 @@
         <v>1.01</v>
       </c>
       <c r="I14" s="1">
-        <v>0.18360000000000001</v>
+        <v>0.19439999999999999</v>
+      </c>
+      <c r="K14">
+        <f>E14*100</f>
+        <v>73</v>
       </c>
       <c r="L14">
-        <f>E14*100</f>
-        <v>71</v>
-      </c>
-      <c r="M14">
         <f>F14*100</f>
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.15">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -1108,13 +1102,13 @@
         <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E15">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="F15">
-        <v>0.68</v>
+        <v>0.62</v>
       </c>
       <c r="G15" t="s">
         <v>13</v>
@@ -1123,18 +1117,18 @@
         <v>1.01</v>
       </c>
       <c r="I15" s="1">
-        <v>0.26350000000000001</v>
+        <v>0.18240000000000001</v>
+      </c>
+      <c r="K15">
+        <f>E15*100</f>
+        <v>72</v>
       </c>
       <c r="L15">
-        <f>E15*100</f>
-        <v>78</v>
-      </c>
-      <c r="M15">
         <f>F15*100</f>
-        <v>68</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.15">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -1145,13 +1139,13 @@
         <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="E16">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="F16">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
@@ -1160,35 +1154,35 @@
         <v>1.01</v>
       </c>
       <c r="I16" s="1">
-        <v>0.18840000000000001</v>
+        <v>0.25469999999999998</v>
+      </c>
+      <c r="K16">
+        <f>E16*100</f>
+        <v>74</v>
       </c>
       <c r="L16">
-        <f>E16*100</f>
-        <v>76</v>
-      </c>
-      <c r="M16">
         <f>F16*100</f>
-        <v>66</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.15">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>29</v>
       </c>
       <c r="B17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" t="s">
         <v>54</v>
       </c>
-      <c r="C17" t="s">
-        <v>55</v>
-      </c>
       <c r="D17" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="E17">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="F17">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="G17" t="s">
         <v>13</v>
@@ -1197,29 +1191,29 @@
         <v>1.01</v>
       </c>
       <c r="I17" s="1">
-        <v>0.20030000000000001</v>
+        <v>0.1842</v>
+      </c>
+      <c r="K17">
+        <f>E17*100</f>
+        <v>82</v>
       </c>
       <c r="L17">
-        <f>E17*100</f>
-        <v>81</v>
-      </c>
-      <c r="M17">
         <f>F17*100</f>
-        <v>71</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.15">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>29</v>
       </c>
       <c r="B18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" t="s">
         <v>56</v>
       </c>
-      <c r="C18" t="s">
-        <v>57</v>
-      </c>
       <c r="D18" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="E18">
         <v>0.81</v>
@@ -1234,35 +1228,35 @@
         <v>1.01</v>
       </c>
       <c r="I18" s="1">
-        <v>0.18229999999999999</v>
-      </c>
-      <c r="L18">
+        <v>0.1993</v>
+      </c>
+      <c r="K18">
         <f>E18*100</f>
         <v>81</v>
       </c>
-      <c r="M18">
+      <c r="L18">
         <f>F18*100</f>
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>29</v>
       </c>
       <c r="B19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" t="s">
         <v>59</v>
       </c>
-      <c r="C19" t="s">
-        <v>60</v>
-      </c>
-      <c r="D19" t="s">
-        <v>61</v>
-      </c>
       <c r="E19">
-        <v>0.69</v>
+        <v>0.81</v>
       </c>
       <c r="F19">
-        <v>0.59</v>
+        <v>0.71</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
@@ -1271,35 +1265,35 @@
         <v>1.01</v>
       </c>
       <c r="I19" s="1">
-        <v>0.23860000000000001</v>
+        <v>0.18410000000000001</v>
+      </c>
+      <c r="K19">
+        <f>E19*100</f>
+        <v>81</v>
       </c>
       <c r="L19">
-        <f>E19*100</f>
-        <v>69</v>
-      </c>
-      <c r="M19">
         <f>F19*100</f>
-        <v>59</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.15">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>29</v>
       </c>
       <c r="B20" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" t="s">
         <v>62</v>
       </c>
-      <c r="C20" t="s">
-        <v>63</v>
-      </c>
-      <c r="D20" t="s">
-        <v>64</v>
-      </c>
       <c r="E20">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="F20">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
@@ -1308,29 +1302,29 @@
         <v>1.01</v>
       </c>
       <c r="I20" s="1">
-        <v>0.18129999999999999</v>
+        <v>0.19919999999999999</v>
+      </c>
+      <c r="K20">
+        <f>E20*100</f>
+        <v>77</v>
       </c>
       <c r="L20">
-        <f>E20*100</f>
-        <v>73</v>
-      </c>
-      <c r="M20">
         <f>F20*100</f>
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.15">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>29</v>
       </c>
       <c r="B21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" t="s">
         <v>65</v>
-      </c>
-      <c r="C21" t="s">
-        <v>66</v>
-      </c>
-      <c r="D21" t="s">
-        <v>67</v>
       </c>
       <c r="E21">
         <v>0.74</v>
@@ -1345,13 +1339,13 @@
         <v>1.01</v>
       </c>
       <c r="I21" s="1">
-        <v>0.2024</v>
-      </c>
-      <c r="L21">
+        <v>0.21510000000000001</v>
+      </c>
+      <c r="K21">
         <f>E21*100</f>
         <v>74</v>
       </c>
-      <c r="M21">
+      <c r="L21">
         <f>F21*100</f>
         <v>64</v>
       </c>

--- a/高波精选组.xlsx
+++ b/高波精选组.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\GopherHK\Fixed Income\结构化产品\HTML 生成\FCN_Watchlist_交接\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEE70054-EC34-4A10-BBDC-05E8301DB636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0D486A7-CAB2-4C86-9EAB-F84E46176006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-340" yWindow="10690" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="68">
   <si>
     <t>区域</t>
   </si>
@@ -65,6 +65,18 @@
     <t>港股</t>
   </si>
   <si>
+    <t>1138 HK</t>
+  </si>
+  <si>
+    <t>中远海能</t>
+  </si>
+  <si>
+    <t>油气中游</t>
+  </si>
+  <si>
+    <t>欧式敲入</t>
+  </si>
+  <si>
     <t>992 HK</t>
   </si>
   <si>
@@ -74,9 +86,6 @@
     <t>计算机硬件</t>
   </si>
   <si>
-    <t>欧式敲入</t>
-  </si>
-  <si>
     <t>1208 HK</t>
   </si>
   <si>
@@ -86,13 +95,13 @@
     <t>铜业</t>
   </si>
   <si>
-    <t>1138 HK</t>
-  </si>
-  <si>
-    <t>中远海能</t>
-  </si>
-  <si>
-    <t>油气中游</t>
+    <t>1888 HK</t>
+  </si>
+  <si>
+    <t>建滔积层板</t>
+  </si>
+  <si>
+    <t>电子元件</t>
   </si>
   <si>
     <t>6869 HK</t>
@@ -104,15 +113,6 @@
     <t>AI光通信</t>
   </si>
   <si>
-    <t>1888 HK</t>
-  </si>
-  <si>
-    <t>建滔积层板</t>
-  </si>
-  <si>
-    <t>电子元件</t>
-  </si>
-  <si>
     <t>522 HK</t>
   </si>
   <si>
@@ -125,12 +125,33 @@
     <t>美股</t>
   </si>
   <si>
+    <t>AMD US</t>
+  </si>
+  <si>
+    <t>超微半导体</t>
+  </si>
+  <si>
+    <t>AI芯片</t>
+  </si>
+  <si>
+    <t>STX US</t>
+  </si>
+  <si>
+    <t>希捷科技</t>
+  </si>
+  <si>
     <t>DELL US</t>
   </si>
   <si>
     <t>戴尔科技</t>
   </si>
   <si>
+    <t>TER US</t>
+  </si>
+  <si>
+    <t>泰瑞达</t>
+  </si>
+  <si>
     <t>PLTR US</t>
   </si>
   <si>
@@ -140,6 +161,24 @@
     <t>AI软件</t>
   </si>
   <si>
+    <t>MU US</t>
+  </si>
+  <si>
+    <t>美光</t>
+  </si>
+  <si>
+    <t>内存/HBM</t>
+  </si>
+  <si>
+    <t>ALAB US</t>
+  </si>
+  <si>
+    <t>阿斯特拉实验室</t>
+  </si>
+  <si>
+    <t>半导体</t>
+  </si>
+  <si>
     <t>HPE US</t>
   </si>
   <si>
@@ -149,28 +188,37 @@
     <t>通信设备</t>
   </si>
   <si>
-    <t>MU US</t>
-  </si>
-  <si>
-    <t>美光</t>
-  </si>
-  <si>
-    <t>内存/HBM</t>
-  </si>
-  <si>
-    <t>STX US</t>
-  </si>
-  <si>
-    <t>希捷科技</t>
-  </si>
-  <si>
-    <t>NET US</t>
-  </si>
-  <si>
-    <t>Cloudflare</t>
-  </si>
-  <si>
-    <t>基础软件</t>
+    <t>CRDO US</t>
+  </si>
+  <si>
+    <t>Credo</t>
+  </si>
+  <si>
+    <t>AI互联</t>
+  </si>
+  <si>
+    <t>LITE US</t>
+  </si>
+  <si>
+    <t>Lumentum</t>
+  </si>
+  <si>
+    <t>MRVL US</t>
+  </si>
+  <si>
+    <t>迈威尔科技</t>
+  </si>
+  <si>
+    <t>客制硅/互联</t>
+  </si>
+  <si>
+    <t>FIX US</t>
+  </si>
+  <si>
+    <t>美国舒适系统</t>
+  </si>
+  <si>
+    <t>工程与建筑</t>
   </si>
   <si>
     <t>HOOD US</t>
@@ -180,48 +228,6 @@
   </si>
   <si>
     <t>券商/加密</t>
-  </si>
-  <si>
-    <t>TER US</t>
-  </si>
-  <si>
-    <t>泰瑞达</t>
-  </si>
-  <si>
-    <t>LITE US</t>
-  </si>
-  <si>
-    <t>Lumentum</t>
-  </si>
-  <si>
-    <t>PANW US</t>
-  </si>
-  <si>
-    <t>Palo Alto Networks</t>
-  </si>
-  <si>
-    <t>NOW US</t>
-  </si>
-  <si>
-    <t>ServiceNow</t>
-  </si>
-  <si>
-    <t>AMD US</t>
-  </si>
-  <si>
-    <t>超微半导体</t>
-  </si>
-  <si>
-    <t>AI芯片</t>
-  </si>
-  <si>
-    <t>FIX US</t>
-  </si>
-  <si>
-    <t>美国舒适系统</t>
-  </si>
-  <si>
-    <t>工程与建筑</t>
   </si>
   <si>
     <t>CVNA US</t>
@@ -578,10 +584,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -610,7 +616,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -624,10 +630,10 @@
         <v>12</v>
       </c>
       <c r="E2">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="F2">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="G2" t="s">
         <v>13</v>
@@ -636,18 +642,10 @@
         <v>1.01</v>
       </c>
       <c r="I2" s="1">
-        <v>0.2024</v>
-      </c>
-      <c r="K2">
-        <f>E2*100</f>
-        <v>78</v>
-      </c>
-      <c r="L2">
-        <f>F2*100</f>
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.15">
+        <v>0.18490000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -661,10 +659,10 @@
         <v>16</v>
       </c>
       <c r="E3">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="F3">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
@@ -673,18 +671,10 @@
         <v>1.01</v>
       </c>
       <c r="I3" s="1">
-        <v>0.11890000000000001</v>
-      </c>
-      <c r="K3">
-        <f>E3*100</f>
-        <v>75</v>
-      </c>
-      <c r="L3">
-        <f>F3*100</f>
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.15">
+        <v>0.19800000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -710,18 +700,10 @@
         <v>1.01</v>
       </c>
       <c r="I4" s="1">
-        <v>0.16819999999999999</v>
-      </c>
-      <c r="K4">
-        <f>E4*100</f>
-        <v>76</v>
-      </c>
-      <c r="L4">
-        <f>F4*100</f>
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.15">
+        <v>0.1056</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -735,10 +717,10 @@
         <v>22</v>
       </c>
       <c r="E5">
-        <v>0.61</v>
+        <v>0.5</v>
       </c>
       <c r="F5">
-        <v>0.51</v>
+        <v>0.4</v>
       </c>
       <c r="G5" t="s">
         <v>13</v>
@@ -747,18 +729,10 @@
         <v>1.01</v>
       </c>
       <c r="I5" s="1">
-        <v>0.25380000000000003</v>
-      </c>
-      <c r="K5">
-        <f>E5*100</f>
-        <v>61</v>
-      </c>
-      <c r="L5">
-        <f>F5*100</f>
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.15">
+        <v>7.6300000000000007E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -772,10 +746,10 @@
         <v>25</v>
       </c>
       <c r="E6">
-        <v>0.5</v>
+        <v>0.74</v>
       </c>
       <c r="F6">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -784,18 +758,10 @@
         <v>1.01</v>
       </c>
       <c r="I6" s="1">
-        <v>9.3700000000000006E-2</v>
-      </c>
-      <c r="K6">
-        <f>E6*100</f>
-        <v>50</v>
-      </c>
-      <c r="L6">
-        <f>F6*100</f>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.15">
+        <v>0.39979999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -809,10 +775,10 @@
         <v>28</v>
       </c>
       <c r="E7">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="F7">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -821,18 +787,10 @@
         <v>1.01</v>
       </c>
       <c r="I7" s="1">
-        <v>0.1605</v>
-      </c>
-      <c r="K7">
-        <f>E7*100</f>
-        <v>73</v>
-      </c>
-      <c r="L7">
-        <f>F7*100</f>
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.15">
+        <v>0.16919999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -843,13 +801,13 @@
         <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E8">
-        <v>0.72</v>
+        <v>0.81</v>
       </c>
       <c r="F8">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -858,35 +816,27 @@
         <v>1.01</v>
       </c>
       <c r="I8" s="1">
-        <v>0.19059999999999999</v>
-      </c>
-      <c r="K8">
-        <f>E8*100</f>
-        <v>72</v>
-      </c>
-      <c r="L8">
-        <f>F8*100</f>
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.15">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="E9">
-        <v>0.8</v>
+        <v>0.71</v>
       </c>
       <c r="F9">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -895,18 +845,10 @@
         <v>1.01</v>
       </c>
       <c r="I9" s="1">
-        <v>0.19980000000000001</v>
-      </c>
-      <c r="K9">
-        <f>E9*100</f>
-        <v>80</v>
-      </c>
-      <c r="L9">
-        <f>F9*100</f>
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.15">
+        <v>0.19239999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -917,7 +859,7 @@
         <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="E10">
         <v>0.73</v>
@@ -932,184 +874,144 @@
         <v>1.01</v>
       </c>
       <c r="I10" s="1">
-        <v>0.1734</v>
-      </c>
-      <c r="K10">
-        <f>E10*100</f>
-        <v>73</v>
-      </c>
-      <c r="L10">
-        <f>F10*100</f>
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.15">
+        <v>0.1943</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>29</v>
       </c>
       <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" t="s">
         <v>38</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11">
+        <v>0.72</v>
+      </c>
+      <c r="F11">
+        <v>0.62</v>
+      </c>
+      <c r="G11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11">
+        <v>1.01</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0.19650000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" t="s">
         <v>39</v>
       </c>
-      <c r="D11" t="s">
+      <c r="C12" t="s">
         <v>40</v>
       </c>
-      <c r="E11">
+      <c r="D12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12">
+        <v>0.81</v>
+      </c>
+      <c r="F12">
+        <v>0.71</v>
+      </c>
+      <c r="G12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12">
+        <v>1.01</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0.21249999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13">
         <v>0.79</v>
       </c>
-      <c r="F11">
+      <c r="F13">
         <v>0.69</v>
       </c>
-      <c r="G11" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11">
-        <v>1.01</v>
-      </c>
-      <c r="I11" s="1">
-        <v>0.18279999999999999</v>
-      </c>
-      <c r="K11">
-        <f>E11*100</f>
-        <v>79</v>
-      </c>
-      <c r="L11">
-        <f>F11*100</f>
-        <v>69</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12">
-        <v>0.71</v>
-      </c>
-      <c r="F12">
-        <v>0.61</v>
-      </c>
-      <c r="G12" t="s">
-        <v>13</v>
-      </c>
-      <c r="H12">
-        <v>1.01</v>
-      </c>
-      <c r="I12" s="1">
-        <v>0.1993</v>
-      </c>
-      <c r="K12">
-        <f>E12*100</f>
-        <v>71</v>
-      </c>
-      <c r="L12">
-        <f>F12*100</f>
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A13" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="G13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13">
+        <v>1.01</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0.1951</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" t="s">
         <v>45</v>
       </c>
-      <c r="E13">
-        <v>0.76</v>
-      </c>
-      <c r="F13">
-        <v>0.66</v>
-      </c>
-      <c r="G13" t="s">
-        <v>13</v>
-      </c>
-      <c r="H13">
-        <v>1.01</v>
-      </c>
-      <c r="I13" s="1">
-        <v>0.20080000000000001</v>
-      </c>
-      <c r="K13">
-        <f>E13*100</f>
-        <v>76</v>
-      </c>
-      <c r="L13">
-        <f>F13*100</f>
-        <v>66</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>46</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>47</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14">
+        <v>0.7</v>
+      </c>
+      <c r="F14">
+        <v>0.6</v>
+      </c>
+      <c r="G14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14">
+        <v>1.01</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0.25580000000000003</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" t="s">
         <v>48</v>
       </c>
-      <c r="E14">
+      <c r="C15" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15">
         <v>0.73</v>
       </c>
-      <c r="F14">
+      <c r="F15">
         <v>0.63</v>
       </c>
-      <c r="G14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H14">
-        <v>1.01</v>
-      </c>
-      <c r="I14" s="1">
-        <v>0.19439999999999999</v>
-      </c>
-      <c r="K14">
-        <f>E14*100</f>
-        <v>73</v>
-      </c>
-      <c r="L14">
-        <f>F14*100</f>
-        <v>63</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" t="s">
-        <v>49</v>
-      </c>
-      <c r="C15" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15">
-        <v>0.72</v>
-      </c>
-      <c r="F15">
-        <v>0.62</v>
-      </c>
       <c r="G15" t="s">
         <v>13</v>
       </c>
@@ -1117,18 +1019,10 @@
         <v>1.01</v>
       </c>
       <c r="I15" s="1">
-        <v>0.18240000000000001</v>
-      </c>
-      <c r="K15">
-        <f>E15*100</f>
-        <v>72</v>
-      </c>
-      <c r="L15">
-        <f>F15*100</f>
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.15">
+        <v>0.18110000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -1139,13 +1033,13 @@
         <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="E16">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="F16">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
@@ -1154,146 +1048,114 @@
         <v>1.01</v>
       </c>
       <c r="I16" s="1">
-        <v>0.25469999999999998</v>
-      </c>
-      <c r="K16">
-        <f>E16*100</f>
-        <v>74</v>
-      </c>
-      <c r="L16">
-        <f>F16*100</f>
+        <v>0.24610000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17">
+        <v>0.75</v>
+      </c>
+      <c r="F17">
+        <v>0.65</v>
+      </c>
+      <c r="G17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17">
+        <v>1.01</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0.2581</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18">
+        <v>0.73</v>
+      </c>
+      <c r="F18">
+        <v>0.63</v>
+      </c>
+      <c r="G18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18">
+        <v>1.01</v>
+      </c>
+      <c r="I18" s="1">
+        <v>0.1822</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A19" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19">
+        <v>0.78</v>
+      </c>
+      <c r="F19">
+        <v>0.68</v>
+      </c>
+      <c r="G19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19">
+        <v>1.01</v>
+      </c>
+      <c r="I19" s="1">
+        <v>0.20119999999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A20" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A17" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" t="s">
-        <v>53</v>
-      </c>
-      <c r="C17" t="s">
-        <v>54</v>
-      </c>
-      <c r="D17" t="s">
-        <v>45</v>
-      </c>
-      <c r="E17">
-        <v>0.82</v>
-      </c>
-      <c r="F17">
-        <v>0.72</v>
-      </c>
-      <c r="G17" t="s">
-        <v>13</v>
-      </c>
-      <c r="H17">
-        <v>1.01</v>
-      </c>
-      <c r="I17" s="1">
-        <v>0.1842</v>
-      </c>
-      <c r="K17">
-        <f>E17*100</f>
-        <v>82</v>
-      </c>
-      <c r="L17">
-        <f>F17*100</f>
-        <v>72</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A18" t="s">
-        <v>29</v>
-      </c>
-      <c r="B18" t="s">
-        <v>55</v>
-      </c>
-      <c r="C18" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" t="s">
-        <v>34</v>
-      </c>
-      <c r="E18">
-        <v>0.81</v>
-      </c>
-      <c r="F18">
-        <v>0.71</v>
-      </c>
-      <c r="G18" t="s">
-        <v>13</v>
-      </c>
-      <c r="H18">
-        <v>1.01</v>
-      </c>
-      <c r="I18" s="1">
-        <v>0.1993</v>
-      </c>
-      <c r="K18">
-        <f>E18*100</f>
-        <v>81</v>
-      </c>
-      <c r="L18">
-        <f>F18*100</f>
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A19" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" t="s">
-        <v>57</v>
-      </c>
-      <c r="C19" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" t="s">
-        <v>59</v>
-      </c>
-      <c r="E19">
-        <v>0.81</v>
-      </c>
-      <c r="F19">
-        <v>0.71</v>
-      </c>
-      <c r="G19" t="s">
-        <v>13</v>
-      </c>
-      <c r="H19">
-        <v>1.01</v>
-      </c>
-      <c r="I19" s="1">
-        <v>0.18410000000000001</v>
-      </c>
-      <c r="K19">
-        <f>E19*100</f>
-        <v>81</v>
-      </c>
-      <c r="L19">
-        <f>F19*100</f>
-        <v>71</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A20" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" t="s">
-        <v>60</v>
-      </c>
-      <c r="C20" t="s">
-        <v>61</v>
-      </c>
-      <c r="D20" t="s">
-        <v>62</v>
-      </c>
       <c r="E20">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="F20">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
@@ -1302,29 +1164,21 @@
         <v>1.01</v>
       </c>
       <c r="I20" s="1">
-        <v>0.19919999999999999</v>
-      </c>
-      <c r="K20">
-        <f>E20*100</f>
-        <v>77</v>
-      </c>
-      <c r="L20">
-        <f>F20*100</f>
+        <v>0.20699999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" t="s">
         <v>67</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A21" t="s">
-        <v>29</v>
-      </c>
-      <c r="B21" t="s">
-        <v>63</v>
-      </c>
-      <c r="C21" t="s">
-        <v>64</v>
-      </c>
-      <c r="D21" t="s">
-        <v>65</v>
       </c>
       <c r="E21">
         <v>0.74</v>
@@ -1339,15 +1193,7 @@
         <v>1.01</v>
       </c>
       <c r="I21" s="1">
-        <v>0.21510000000000001</v>
-      </c>
-      <c r="K21">
-        <f>E21*100</f>
-        <v>74</v>
-      </c>
-      <c r="L21">
-        <f>F21*100</f>
-        <v>64</v>
+        <v>0.21160000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/高波精选组.xlsx
+++ b/高波精选组.xlsx
@@ -8,32 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\GopherHK\Fixed Income\结构化产品\HTML 生成\FCN_Watchlist_交接\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0D486A7-CAB2-4C86-9EAB-F84E46176006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C604A84-D5B3-4C8B-A75B-83C4F287AABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-340" yWindow="10690" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="66">
   <si>
     <t>区域</t>
   </si>
@@ -86,6 +73,15 @@
     <t>计算机硬件</t>
   </si>
   <si>
+    <t>6869 HK</t>
+  </si>
+  <si>
+    <t>长飞光纤</t>
+  </si>
+  <si>
+    <t>AI光通信</t>
+  </si>
+  <si>
     <t>1208 HK</t>
   </si>
   <si>
@@ -104,15 +100,6 @@
     <t>电子元件</t>
   </si>
   <si>
-    <t>6869 HK</t>
-  </si>
-  <si>
-    <t>长飞光纤</t>
-  </si>
-  <si>
-    <t>AI光通信</t>
-  </si>
-  <si>
     <t>522 HK</t>
   </si>
   <si>
@@ -125,19 +112,52 @@
     <t>美股</t>
   </si>
   <si>
-    <t>AMD US</t>
-  </si>
-  <si>
-    <t>超微半导体</t>
-  </si>
-  <si>
-    <t>AI芯片</t>
-  </si>
-  <si>
-    <t>STX US</t>
-  </si>
-  <si>
-    <t>希捷科技</t>
+    <t>TER US</t>
+  </si>
+  <si>
+    <t>泰瑞达</t>
+  </si>
+  <si>
+    <t>MRVL US</t>
+  </si>
+  <si>
+    <t>迈威尔科技</t>
+  </si>
+  <si>
+    <t>客制硅/互联</t>
+  </si>
+  <si>
+    <t>MU US</t>
+  </si>
+  <si>
+    <t>美光</t>
+  </si>
+  <si>
+    <t>内存/HBM</t>
+  </si>
+  <si>
+    <t>CLS US</t>
+  </si>
+  <si>
+    <t>天弘科技</t>
+  </si>
+  <si>
+    <t>MPWR US</t>
+  </si>
+  <si>
+    <t>芯源系统</t>
+  </si>
+  <si>
+    <t>半导体</t>
+  </si>
+  <si>
+    <t>HPE US</t>
+  </si>
+  <si>
+    <t>慧与科技</t>
+  </si>
+  <si>
+    <t>通信设备</t>
   </si>
   <si>
     <t>DELL US</t>
@@ -146,46 +166,16 @@
     <t>戴尔科技</t>
   </si>
   <si>
-    <t>TER US</t>
-  </si>
-  <si>
-    <t>泰瑞达</t>
-  </si>
-  <si>
-    <t>PLTR US</t>
-  </si>
-  <si>
-    <t>帕兰提尔</t>
-  </si>
-  <si>
-    <t>AI软件</t>
-  </si>
-  <si>
-    <t>MU US</t>
-  </si>
-  <si>
-    <t>美光</t>
-  </si>
-  <si>
-    <t>内存/HBM</t>
-  </si>
-  <si>
     <t>ALAB US</t>
   </si>
   <si>
     <t>阿斯特拉实验室</t>
   </si>
   <si>
-    <t>半导体</t>
-  </si>
-  <si>
-    <t>HPE US</t>
-  </si>
-  <si>
-    <t>慧与科技</t>
-  </si>
-  <si>
-    <t>通信设备</t>
+    <t>LRCX US</t>
+  </si>
+  <si>
+    <t>泛林集团</t>
   </si>
   <si>
     <t>CRDO US</t>
@@ -203,15 +193,6 @@
     <t>Lumentum</t>
   </si>
   <si>
-    <t>MRVL US</t>
-  </si>
-  <si>
-    <t>迈威尔科技</t>
-  </si>
-  <si>
-    <t>客制硅/互联</t>
-  </si>
-  <si>
     <t>FIX US</t>
   </si>
   <si>
@@ -221,6 +202,15 @@
     <t>工程与建筑</t>
   </si>
   <si>
+    <t>CVNA US</t>
+  </si>
+  <si>
+    <t>卡瓦纳</t>
+  </si>
+  <si>
+    <t>汽车与卡车经销</t>
+  </si>
+  <si>
     <t>HOOD US</t>
   </si>
   <si>
@@ -228,15 +218,6 @@
   </si>
   <si>
     <t>券商/加密</t>
-  </si>
-  <si>
-    <t>CVNA US</t>
-  </si>
-  <si>
-    <t>卡瓦纳</t>
-  </si>
-  <si>
-    <t>汽车与卡车经销</t>
   </si>
 </sst>
 </file>
@@ -642,7 +623,7 @@
         <v>1.01</v>
       </c>
       <c r="I2" s="1">
-        <v>0.18490000000000001</v>
+        <v>0.19739999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.15">
@@ -659,10 +640,10 @@
         <v>16</v>
       </c>
       <c r="E3">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="F3">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
@@ -671,7 +652,7 @@
         <v>1.01</v>
       </c>
       <c r="I3" s="1">
-        <v>0.19800000000000001</v>
+        <v>0.19520000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.15">
@@ -688,10 +669,10 @@
         <v>19</v>
       </c>
       <c r="E4">
-        <v>0.76</v>
+        <v>0.6</v>
       </c>
       <c r="F4">
-        <v>0.66</v>
+        <v>0.5</v>
       </c>
       <c r="G4" t="s">
         <v>13</v>
@@ -700,7 +681,7 @@
         <v>1.01</v>
       </c>
       <c r="I4" s="1">
-        <v>0.1056</v>
+        <v>0.2666</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.15">
@@ -717,10 +698,10 @@
         <v>22</v>
       </c>
       <c r="E5">
-        <v>0.5</v>
+        <v>0.77</v>
       </c>
       <c r="F5">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="G5" t="s">
         <v>13</v>
@@ -729,7 +710,7 @@
         <v>1.01</v>
       </c>
       <c r="I5" s="1">
-        <v>7.6300000000000007E-2</v>
+        <v>0.1095</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.15">
@@ -746,10 +727,10 @@
         <v>25</v>
       </c>
       <c r="E6">
-        <v>0.74</v>
+        <v>0.5</v>
       </c>
       <c r="F6">
-        <v>0.64</v>
+        <v>0.4</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -758,7 +739,7 @@
         <v>1.01</v>
       </c>
       <c r="I6" s="1">
-        <v>0.39979999999999999</v>
+        <v>7.6899999999999996E-2</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.15">
@@ -775,10 +756,10 @@
         <v>28</v>
       </c>
       <c r="E7">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="F7">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -787,7 +768,7 @@
         <v>1.01</v>
       </c>
       <c r="I7" s="1">
-        <v>0.16919999999999999</v>
+        <v>0.1537</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.15">
@@ -801,13 +782,13 @@
         <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E8">
-        <v>0.81</v>
+        <v>0.71</v>
       </c>
       <c r="F8">
-        <v>0.71</v>
+        <v>0.61</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -816,7 +797,7 @@
         <v>1.01</v>
       </c>
       <c r="I8" s="1">
-        <v>0.2</v>
+        <v>0.2029</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.15">
@@ -824,19 +805,19 @@
         <v>29</v>
       </c>
       <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
         <v>33</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>34</v>
       </c>
-      <c r="D9" t="s">
-        <v>16</v>
-      </c>
       <c r="E9">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="F9">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -845,7 +826,7 @@
         <v>1.01</v>
       </c>
       <c r="I9" s="1">
-        <v>0.19239999999999999</v>
+        <v>0.18210000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.15">
@@ -859,13 +840,13 @@
         <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="E10">
-        <v>0.73</v>
+        <v>0.84</v>
       </c>
       <c r="F10">
-        <v>0.63</v>
+        <v>0.74</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -874,7 +855,7 @@
         <v>1.01</v>
       </c>
       <c r="I10" s="1">
-        <v>0.1943</v>
+        <v>0.18609999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.15">
@@ -882,13 +863,13 @@
         <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E11">
         <v>0.72</v>
@@ -903,7 +884,7 @@
         <v>1.01</v>
       </c>
       <c r="I11" s="1">
-        <v>0.19650000000000001</v>
+        <v>0.20569999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.15">
@@ -911,19 +892,19 @@
         <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E12">
-        <v>0.81</v>
+        <v>0.8</v>
       </c>
       <c r="F12">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
@@ -932,7 +913,7 @@
         <v>1.01</v>
       </c>
       <c r="I12" s="1">
-        <v>0.21249999999999999</v>
+        <v>0.19120000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.15">
@@ -940,19 +921,19 @@
         <v>29</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E13">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="F13">
-        <v>0.69</v>
+        <v>0.63</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
@@ -961,7 +942,7 @@
         <v>1.01</v>
       </c>
       <c r="I13" s="1">
-        <v>0.1951</v>
+        <v>0.18110000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.15">
@@ -969,19 +950,19 @@
         <v>29</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="E14">
-        <v>0.7</v>
+        <v>0.74</v>
       </c>
       <c r="F14">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="G14" t="s">
         <v>13</v>
@@ -990,7 +971,7 @@
         <v>1.01</v>
       </c>
       <c r="I14" s="1">
-        <v>0.25580000000000003</v>
+        <v>0.19539999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.15">
@@ -1004,13 +985,13 @@
         <v>49</v>
       </c>
       <c r="D15" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E15">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="F15">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="G15" t="s">
         <v>13</v>
@@ -1019,7 +1000,7 @@
         <v>1.01</v>
       </c>
       <c r="I15" s="1">
-        <v>0.18110000000000001</v>
+        <v>0.25829999999999997</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.15">
@@ -1027,19 +1008,19 @@
         <v>29</v>
       </c>
       <c r="B16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" t="s">
         <v>51</v>
       </c>
-      <c r="C16" t="s">
-        <v>52</v>
-      </c>
       <c r="D16" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="E16">
-        <v>0.7</v>
+        <v>0.78</v>
       </c>
       <c r="F16">
-        <v>0.6</v>
+        <v>0.68</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
@@ -1048,7 +1029,7 @@
         <v>1.01</v>
       </c>
       <c r="I16" s="1">
-        <v>0.24610000000000001</v>
+        <v>0.1958</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.15">
@@ -1056,19 +1037,19 @@
         <v>29</v>
       </c>
       <c r="B17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" t="s">
         <v>54</v>
       </c>
-      <c r="C17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" t="s">
-        <v>50</v>
-      </c>
       <c r="E17">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="F17">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="G17" t="s">
         <v>13</v>
@@ -1077,7 +1058,7 @@
         <v>1.01</v>
       </c>
       <c r="I17" s="1">
-        <v>0.2581</v>
+        <v>0.25380000000000003</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.15">
@@ -1085,19 +1066,19 @@
         <v>29</v>
       </c>
       <c r="B18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" t="s">
         <v>56</v>
       </c>
-      <c r="C18" t="s">
-        <v>57</v>
-      </c>
       <c r="D18" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="E18">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="F18">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="G18" t="s">
         <v>13</v>
@@ -1106,7 +1087,7 @@
         <v>1.01</v>
       </c>
       <c r="I18" s="1">
-        <v>0.1822</v>
+        <v>0.2571</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.15">
@@ -1114,19 +1095,19 @@
         <v>29</v>
       </c>
       <c r="B19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" t="s">
         <v>59</v>
       </c>
-      <c r="C19" t="s">
-        <v>60</v>
-      </c>
-      <c r="D19" t="s">
-        <v>61</v>
-      </c>
       <c r="E19">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="F19">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
@@ -1135,7 +1116,7 @@
         <v>1.01</v>
       </c>
       <c r="I19" s="1">
-        <v>0.20119999999999999</v>
+        <v>0.21060000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.15">
@@ -1143,19 +1124,19 @@
         <v>29</v>
       </c>
       <c r="B20" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" t="s">
         <v>62</v>
       </c>
-      <c r="C20" t="s">
-        <v>63</v>
-      </c>
-      <c r="D20" t="s">
-        <v>64</v>
-      </c>
       <c r="E20">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="F20">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
@@ -1164,7 +1145,7 @@
         <v>1.01</v>
       </c>
       <c r="I20" s="1">
-        <v>0.20699999999999999</v>
+        <v>0.23039999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.15">
@@ -1172,19 +1153,19 @@
         <v>29</v>
       </c>
       <c r="B21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" t="s">
         <v>65</v>
       </c>
-      <c r="C21" t="s">
-        <v>66</v>
-      </c>
-      <c r="D21" t="s">
-        <v>67</v>
-      </c>
       <c r="E21">
-        <v>0.74</v>
+        <v>0.77</v>
       </c>
       <c r="F21">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="G21" t="s">
         <v>13</v>
@@ -1193,7 +1174,7 @@
         <v>1.01</v>
       </c>
       <c r="I21" s="1">
-        <v>0.21160000000000001</v>
+        <v>0.19769999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/高波精选组.xlsx
+++ b/高波精选组.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\GopherHK\Fixed Income\结构化产品\HTML 生成\FCN_Watchlist_交接\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C604A84-D5B3-4C8B-A75B-83C4F287AABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76EEF939-4914-49DF-8619-E82925C8FAE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="67">
   <si>
     <t>区域</t>
   </si>
@@ -82,15 +82,6 @@
     <t>AI光通信</t>
   </si>
   <si>
-    <t>1208 HK</t>
-  </si>
-  <si>
-    <t>五矿资源</t>
-  </si>
-  <si>
-    <t>铜业</t>
-  </si>
-  <si>
     <t>1888 HK</t>
   </si>
   <si>
@@ -109,6 +100,15 @@
     <t>半导体设备与材料</t>
   </si>
   <si>
+    <t>2338 HK</t>
+  </si>
+  <si>
+    <t>潍柴动力</t>
+  </si>
+  <si>
+    <t>汽车制造</t>
+  </si>
+  <si>
     <t>美股</t>
   </si>
   <si>
@@ -127,6 +127,30 @@
     <t>客制硅/互联</t>
   </si>
   <si>
+    <t>HPE US</t>
+  </si>
+  <si>
+    <t>慧与科技</t>
+  </si>
+  <si>
+    <t>通信设备</t>
+  </si>
+  <si>
+    <t>DELL US</t>
+  </si>
+  <si>
+    <t>戴尔科技</t>
+  </si>
+  <si>
+    <t>ALAB US</t>
+  </si>
+  <si>
+    <t>阿斯特拉实验室</t>
+  </si>
+  <si>
+    <t>半导体</t>
+  </si>
+  <si>
     <t>MU US</t>
   </si>
   <si>
@@ -136,70 +160,49 @@
     <t>内存/HBM</t>
   </si>
   <si>
+    <t>FIX US</t>
+  </si>
+  <si>
+    <t>美国舒适系统</t>
+  </si>
+  <si>
+    <t>工程与建筑</t>
+  </si>
+  <si>
+    <t>CRDO US</t>
+  </si>
+  <si>
+    <t>Credo</t>
+  </si>
+  <si>
+    <t>AI互联</t>
+  </si>
+  <si>
+    <t>LITE US</t>
+  </si>
+  <si>
+    <t>Lumentum</t>
+  </si>
+  <si>
+    <t>SHOP US</t>
+  </si>
+  <si>
+    <t>Shopify</t>
+  </si>
+  <si>
+    <t>应用软件</t>
+  </si>
+  <si>
+    <t>DDOG US</t>
+  </si>
+  <si>
+    <t>Datadog</t>
+  </si>
+  <si>
     <t>CLS US</t>
   </si>
   <si>
     <t>天弘科技</t>
-  </si>
-  <si>
-    <t>MPWR US</t>
-  </si>
-  <si>
-    <t>芯源系统</t>
-  </si>
-  <si>
-    <t>半导体</t>
-  </si>
-  <si>
-    <t>HPE US</t>
-  </si>
-  <si>
-    <t>慧与科技</t>
-  </si>
-  <si>
-    <t>通信设备</t>
-  </si>
-  <si>
-    <t>DELL US</t>
-  </si>
-  <si>
-    <t>戴尔科技</t>
-  </si>
-  <si>
-    <t>ALAB US</t>
-  </si>
-  <si>
-    <t>阿斯特拉实验室</t>
-  </si>
-  <si>
-    <t>LRCX US</t>
-  </si>
-  <si>
-    <t>泛林集团</t>
-  </si>
-  <si>
-    <t>CRDO US</t>
-  </si>
-  <si>
-    <t>Credo</t>
-  </si>
-  <si>
-    <t>AI互联</t>
-  </si>
-  <si>
-    <t>LITE US</t>
-  </si>
-  <si>
-    <t>Lumentum</t>
-  </si>
-  <si>
-    <t>FIX US</t>
-  </si>
-  <si>
-    <t>美国舒适系统</t>
-  </si>
-  <si>
-    <t>工程与建筑</t>
   </si>
   <si>
     <t>CVNA US</t>
@@ -623,7 +626,7 @@
         <v>1.01</v>
       </c>
       <c r="I2" s="1">
-        <v>0.19739999999999999</v>
+        <v>0.2009</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.15">
@@ -640,10 +643,10 @@
         <v>16</v>
       </c>
       <c r="E3">
-        <v>0.77</v>
+        <v>0.8</v>
       </c>
       <c r="F3">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
@@ -652,7 +655,7 @@
         <v>1.01</v>
       </c>
       <c r="I3" s="1">
-        <v>0.19520000000000001</v>
+        <v>0.19769999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.15">
@@ -669,10 +672,10 @@
         <v>19</v>
       </c>
       <c r="E4">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="F4">
-        <v>0.5</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G4" t="s">
         <v>13</v>
@@ -681,7 +684,7 @@
         <v>1.01</v>
       </c>
       <c r="I4" s="1">
-        <v>0.2666</v>
+        <v>0.29570000000000002</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.15">
@@ -698,10 +701,10 @@
         <v>22</v>
       </c>
       <c r="E5">
-        <v>0.77</v>
+        <v>0.5</v>
       </c>
       <c r="F5">
-        <v>0.67</v>
+        <v>0.4</v>
       </c>
       <c r="G5" t="s">
         <v>13</v>
@@ -710,7 +713,7 @@
         <v>1.01</v>
       </c>
       <c r="I5" s="1">
-        <v>0.1095</v>
+        <v>8.6300000000000002E-2</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.15">
@@ -727,10 +730,10 @@
         <v>25</v>
       </c>
       <c r="E6">
-        <v>0.5</v>
+        <v>0.74</v>
       </c>
       <c r="F6">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -739,7 +742,7 @@
         <v>1.01</v>
       </c>
       <c r="I6" s="1">
-        <v>7.6899999999999996E-2</v>
+        <v>0.121</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.15">
@@ -756,10 +759,10 @@
         <v>28</v>
       </c>
       <c r="E7">
-        <v>0.73</v>
+        <v>0.82</v>
       </c>
       <c r="F7">
-        <v>0.63</v>
+        <v>0.72</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -768,7 +771,7 @@
         <v>1.01</v>
       </c>
       <c r="I7" s="1">
-        <v>0.1537</v>
+        <v>0.20030000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.15">
@@ -782,13 +785,13 @@
         <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E8">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="F8">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -797,7 +800,7 @@
         <v>1.01</v>
       </c>
       <c r="I8" s="1">
-        <v>0.2029</v>
+        <v>0.18790000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.15">
@@ -814,10 +817,10 @@
         <v>34</v>
       </c>
       <c r="E9">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="F9">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -826,7 +829,7 @@
         <v>1.01</v>
       </c>
       <c r="I9" s="1">
-        <v>0.18210000000000001</v>
+        <v>0.18310000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.15">
@@ -843,10 +846,10 @@
         <v>37</v>
       </c>
       <c r="E10">
-        <v>0.84</v>
+        <v>0.73</v>
       </c>
       <c r="F10">
-        <v>0.74</v>
+        <v>0.63</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -855,7 +858,7 @@
         <v>1.01</v>
       </c>
       <c r="I10" s="1">
-        <v>0.18609999999999999</v>
+        <v>0.1691</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.15">
@@ -869,13 +872,13 @@
         <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E11">
-        <v>0.72</v>
+        <v>0.76</v>
       </c>
       <c r="F11">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
@@ -884,7 +887,7 @@
         <v>1.01</v>
       </c>
       <c r="I11" s="1">
-        <v>0.20569999999999999</v>
+        <v>0.19769999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.15">
@@ -901,10 +904,10 @@
         <v>42</v>
       </c>
       <c r="E12">
-        <v>0.8</v>
+        <v>0.72</v>
       </c>
       <c r="F12">
-        <v>0.7</v>
+        <v>0.62</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
@@ -913,7 +916,7 @@
         <v>1.01</v>
       </c>
       <c r="I12" s="1">
-        <v>0.19120000000000001</v>
+        <v>0.2495</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.15">
@@ -930,10 +933,10 @@
         <v>45</v>
       </c>
       <c r="E13">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="F13">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
@@ -942,7 +945,7 @@
         <v>1.01</v>
       </c>
       <c r="I13" s="1">
-        <v>0.18110000000000001</v>
+        <v>0.13880000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.15">
@@ -956,13 +959,13 @@
         <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="E14">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="F14">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="G14" t="s">
         <v>13</v>
@@ -971,7 +974,7 @@
         <v>1.01</v>
       </c>
       <c r="I14" s="1">
-        <v>0.19539999999999999</v>
+        <v>0.2059</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.15">
@@ -979,19 +982,19 @@
         <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="E15">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="F15">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="G15" t="s">
         <v>13</v>
@@ -1000,7 +1003,7 @@
         <v>1.01</v>
       </c>
       <c r="I15" s="1">
-        <v>0.25829999999999997</v>
+        <v>0.26819999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.15">
@@ -1008,19 +1011,19 @@
         <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E16">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="F16">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
@@ -1029,7 +1032,7 @@
         <v>1.01</v>
       </c>
       <c r="I16" s="1">
-        <v>0.1958</v>
+        <v>0.2457</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.15">
@@ -1037,19 +1040,19 @@
         <v>29</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E17">
-        <v>0.7</v>
+        <v>0.81</v>
       </c>
       <c r="F17">
-        <v>0.6</v>
+        <v>0.71</v>
       </c>
       <c r="G17" t="s">
         <v>13</v>
@@ -1058,7 +1061,7 @@
         <v>1.01</v>
       </c>
       <c r="I17" s="1">
-        <v>0.25380000000000003</v>
+        <v>0.19980000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.15">
@@ -1066,19 +1069,19 @@
         <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C18" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" t="s">
         <v>56</v>
       </c>
-      <c r="D18" t="s">
-        <v>45</v>
-      </c>
       <c r="E18">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="F18">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="G18" t="s">
         <v>13</v>
@@ -1087,7 +1090,7 @@
         <v>1.01</v>
       </c>
       <c r="I18" s="1">
-        <v>0.2571</v>
+        <v>0.2014</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.15">
@@ -1095,19 +1098,19 @@
         <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C19" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D19" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="E19">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="F19">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
@@ -1116,7 +1119,7 @@
         <v>1.01</v>
       </c>
       <c r="I19" s="1">
-        <v>0.21060000000000001</v>
+        <v>0.1973</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.15">
@@ -1124,13 +1127,13 @@
         <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C20" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E20">
         <v>0.74</v>
@@ -1145,7 +1148,7 @@
         <v>1.01</v>
       </c>
       <c r="I20" s="1">
-        <v>0.23039999999999999</v>
+        <v>0.21160000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.15">
@@ -1153,19 +1156,19 @@
         <v>29</v>
       </c>
       <c r="B21" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E21">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="F21">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="G21" t="s">
         <v>13</v>
@@ -1174,7 +1177,7 @@
         <v>1.01</v>
       </c>
       <c r="I21" s="1">
-        <v>0.19769999999999999</v>
+        <v>0.20180000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/高波精选组.xlsx
+++ b/高波精选组.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\GopherHK\Fixed Income\结构化产品\HTML 生成\FCN_Watchlist_交接\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76EEF939-4914-49DF-8619-E82925C8FAE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66445CB3-693D-4137-8D17-94653BB1EE40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="68">
   <si>
     <t>区域</t>
   </si>
@@ -52,6 +52,18 @@
     <t>港股</t>
   </si>
   <si>
+    <t>1888 HK</t>
+  </si>
+  <si>
+    <t>建滔积层板</t>
+  </si>
+  <si>
+    <t>电子元件</t>
+  </si>
+  <si>
+    <t>欧式敲入</t>
+  </si>
+  <si>
     <t>1138 HK</t>
   </si>
   <si>
@@ -61,7 +73,13 @@
     <t>油气中游</t>
   </si>
   <si>
-    <t>欧式敲入</t>
+    <t>6869 HK</t>
+  </si>
+  <si>
+    <t>长飞光纤</t>
+  </si>
+  <si>
+    <t>AI光通信</t>
   </si>
   <si>
     <t>992 HK</t>
@@ -73,24 +91,6 @@
     <t>计算机硬件</t>
   </si>
   <si>
-    <t>6869 HK</t>
-  </si>
-  <si>
-    <t>长飞光纤</t>
-  </si>
-  <si>
-    <t>AI光通信</t>
-  </si>
-  <si>
-    <t>1888 HK</t>
-  </si>
-  <si>
-    <t>建滔积层板</t>
-  </si>
-  <si>
-    <t>电子元件</t>
-  </si>
-  <si>
     <t>522 HK</t>
   </si>
   <si>
@@ -100,33 +100,66 @@
     <t>半导体设备与材料</t>
   </si>
   <si>
-    <t>2338 HK</t>
-  </si>
-  <si>
-    <t>潍柴动力</t>
-  </si>
-  <si>
-    <t>汽车制造</t>
+    <t>3993 HK</t>
+  </si>
+  <si>
+    <t>洛阳钼业</t>
+  </si>
+  <si>
+    <t>工业金属与采矿</t>
   </si>
   <si>
     <t>美股</t>
   </si>
   <si>
+    <t>SHOP US</t>
+  </si>
+  <si>
+    <t>Shopify</t>
+  </si>
+  <si>
+    <t>应用软件</t>
+  </si>
+  <si>
+    <t>MRVL US</t>
+  </si>
+  <si>
+    <t>迈威尔科技</t>
+  </si>
+  <si>
+    <t>客制硅/互联</t>
+  </si>
+  <si>
+    <t>DDOG US</t>
+  </si>
+  <si>
+    <t>Datadog</t>
+  </si>
+  <si>
+    <t>NET US</t>
+  </si>
+  <si>
+    <t>Cloudflare</t>
+  </si>
+  <si>
+    <t>基础软件</t>
+  </si>
+  <si>
+    <t>ALAB US</t>
+  </si>
+  <si>
+    <t>阿斯特拉实验室</t>
+  </si>
+  <si>
+    <t>半导体</t>
+  </si>
+  <si>
     <t>TER US</t>
   </si>
   <si>
     <t>泰瑞达</t>
   </si>
   <si>
-    <t>MRVL US</t>
-  </si>
-  <si>
-    <t>迈威尔科技</t>
-  </si>
-  <si>
-    <t>客制硅/互联</t>
-  </si>
-  <si>
     <t>HPE US</t>
   </si>
   <si>
@@ -142,13 +175,19 @@
     <t>戴尔科技</t>
   </si>
   <si>
-    <t>ALAB US</t>
-  </si>
-  <si>
-    <t>阿斯特拉实验室</t>
-  </si>
-  <si>
-    <t>半导体</t>
+    <t>CRDO US</t>
+  </si>
+  <si>
+    <t>Credo</t>
+  </si>
+  <si>
+    <t>AI互联</t>
+  </si>
+  <si>
+    <t>CIEN US</t>
+  </si>
+  <si>
+    <t>Ciena</t>
   </si>
   <si>
     <t>MU US</t>
@@ -169,40 +208,13 @@
     <t>工程与建筑</t>
   </si>
   <si>
-    <t>CRDO US</t>
-  </si>
-  <si>
-    <t>Credo</t>
-  </si>
-  <si>
-    <t>AI互联</t>
-  </si>
-  <si>
-    <t>LITE US</t>
-  </si>
-  <si>
-    <t>Lumentum</t>
-  </si>
-  <si>
-    <t>SHOP US</t>
-  </si>
-  <si>
-    <t>Shopify</t>
-  </si>
-  <si>
-    <t>应用软件</t>
-  </si>
-  <si>
-    <t>DDOG US</t>
-  </si>
-  <si>
-    <t>Datadog</t>
-  </si>
-  <si>
-    <t>CLS US</t>
-  </si>
-  <si>
-    <t>天弘科技</t>
+    <t>HOOD US</t>
+  </si>
+  <si>
+    <t>罗宾汉</t>
+  </si>
+  <si>
+    <t>券商/加密</t>
   </si>
   <si>
     <t>CVNA US</t>
@@ -212,15 +224,6 @@
   </si>
   <si>
     <t>汽车与卡车经销</t>
-  </si>
-  <si>
-    <t>HOOD US</t>
-  </si>
-  <si>
-    <t>罗宾汉</t>
-  </si>
-  <si>
-    <t>券商/加密</t>
   </si>
 </sst>
 </file>
@@ -614,10 +617,10 @@
         <v>12</v>
       </c>
       <c r="E2">
-        <v>0.77</v>
+        <v>0.5</v>
       </c>
       <c r="F2">
-        <v>0.67</v>
+        <v>0.4</v>
       </c>
       <c r="G2" t="s">
         <v>13</v>
@@ -626,7 +629,7 @@
         <v>1.01</v>
       </c>
       <c r="I2" s="1">
-        <v>0.2009</v>
+        <v>9.1200000000000003E-2</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.15">
@@ -643,10 +646,10 @@
         <v>16</v>
       </c>
       <c r="E3">
-        <v>0.8</v>
+        <v>0.74</v>
       </c>
       <c r="F3">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
@@ -655,7 +658,7 @@
         <v>1.01</v>
       </c>
       <c r="I3" s="1">
-        <v>0.19769999999999999</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.15">
@@ -684,7 +687,7 @@
         <v>1.01</v>
       </c>
       <c r="I4" s="1">
-        <v>0.29570000000000002</v>
+        <v>0.2979</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.15">
@@ -701,10 +704,10 @@
         <v>22</v>
       </c>
       <c r="E5">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="F5">
-        <v>0.4</v>
+        <v>0.68</v>
       </c>
       <c r="G5" t="s">
         <v>13</v>
@@ -713,7 +716,7 @@
         <v>1.01</v>
       </c>
       <c r="I5" s="1">
-        <v>8.6300000000000002E-2</v>
+        <v>0.21299999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.15">
@@ -730,10 +733,10 @@
         <v>25</v>
       </c>
       <c r="E6">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="F6">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -742,7 +745,7 @@
         <v>1.01</v>
       </c>
       <c r="I6" s="1">
-        <v>0.121</v>
+        <v>0.1399</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.15">
@@ -759,10 +762,10 @@
         <v>28</v>
       </c>
       <c r="E7">
-        <v>0.82</v>
+        <v>0.81</v>
       </c>
       <c r="F7">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -771,7 +774,7 @@
         <v>1.01</v>
       </c>
       <c r="I7" s="1">
-        <v>0.20030000000000001</v>
+        <v>0.14330000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.15">
@@ -785,13 +788,13 @@
         <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E8">
-        <v>0.73</v>
+        <v>0.79</v>
       </c>
       <c r="F8">
-        <v>0.63</v>
+        <v>0.69</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -800,7 +803,7 @@
         <v>1.01</v>
       </c>
       <c r="I8" s="1">
-        <v>0.18790000000000001</v>
+        <v>0.20499999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.15">
@@ -808,13 +811,13 @@
         <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E9">
         <v>0.77</v>
@@ -829,7 +832,7 @@
         <v>1.01</v>
       </c>
       <c r="I9" s="1">
-        <v>0.18310000000000001</v>
+        <v>0.19739999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.15">
@@ -837,19 +840,19 @@
         <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E10">
-        <v>0.73</v>
+        <v>0.76</v>
       </c>
       <c r="F10">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -858,7 +861,7 @@
         <v>1.01</v>
       </c>
       <c r="I10" s="1">
-        <v>0.1691</v>
+        <v>0.20449999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.15">
@@ -872,13 +875,13 @@
         <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="E11">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="F11">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
@@ -887,7 +890,7 @@
         <v>1.01</v>
       </c>
       <c r="I11" s="1">
-        <v>0.19769999999999999</v>
+        <v>0.20749999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.15">
@@ -895,19 +898,19 @@
         <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E12">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="F12">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
@@ -916,7 +919,7 @@
         <v>1.01</v>
       </c>
       <c r="I12" s="1">
-        <v>0.2495</v>
+        <v>0.2616</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.15">
@@ -924,19 +927,19 @@
         <v>29</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="E13">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="F13">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
@@ -945,7 +948,7 @@
         <v>1.01</v>
       </c>
       <c r="I13" s="1">
-        <v>0.13880000000000001</v>
+        <v>0.20030000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.15">
@@ -962,10 +965,10 @@
         <v>48</v>
       </c>
       <c r="E14">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="F14">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="G14" t="s">
         <v>13</v>
@@ -974,7 +977,7 @@
         <v>1.01</v>
       </c>
       <c r="I14" s="1">
-        <v>0.2059</v>
+        <v>0.19620000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.15">
@@ -988,13 +991,13 @@
         <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="E15">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="F15">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="G15" t="s">
         <v>13</v>
@@ -1003,7 +1006,7 @@
         <v>1.01</v>
       </c>
       <c r="I15" s="1">
-        <v>0.26819999999999999</v>
+        <v>0.2001</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.15">
@@ -1011,19 +1014,19 @@
         <v>29</v>
       </c>
       <c r="B16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" t="s">
         <v>52</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>53</v>
       </c>
-      <c r="D16" t="s">
-        <v>37</v>
-      </c>
       <c r="E16">
-        <v>0.77</v>
+        <v>0.73</v>
       </c>
       <c r="F16">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
@@ -1032,7 +1035,7 @@
         <v>1.01</v>
       </c>
       <c r="I16" s="1">
-        <v>0.2457</v>
+        <v>0.27529999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.15">
@@ -1046,13 +1049,13 @@
         <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E17">
-        <v>0.81</v>
+        <v>0.71</v>
       </c>
       <c r="F17">
-        <v>0.71</v>
+        <v>0.61</v>
       </c>
       <c r="G17" t="s">
         <v>13</v>
@@ -1061,7 +1064,7 @@
         <v>1.01</v>
       </c>
       <c r="I17" s="1">
-        <v>0.19980000000000001</v>
+        <v>0.19139999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.15">
@@ -1069,19 +1072,19 @@
         <v>29</v>
       </c>
       <c r="B18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" t="s">
         <v>57</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>58</v>
       </c>
-      <c r="D18" t="s">
-        <v>56</v>
-      </c>
       <c r="E18">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="F18">
-        <v>0.66</v>
+        <v>0.69</v>
       </c>
       <c r="G18" t="s">
         <v>13</v>
@@ -1090,7 +1093,7 @@
         <v>1.01</v>
       </c>
       <c r="I18" s="1">
-        <v>0.2014</v>
+        <v>0.15110000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.15">
@@ -1104,13 +1107,13 @@
         <v>60</v>
       </c>
       <c r="D19" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="E19">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="F19">
-        <v>0.65</v>
+        <v>0.69</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
@@ -1119,7 +1122,7 @@
         <v>1.01</v>
       </c>
       <c r="I19" s="1">
-        <v>0.1973</v>
+        <v>0.20669999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.15">
@@ -1127,19 +1130,19 @@
         <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E20">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="F20">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
@@ -1148,7 +1151,7 @@
         <v>1.01</v>
       </c>
       <c r="I20" s="1">
-        <v>0.21160000000000001</v>
+        <v>0.2026</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.15">
@@ -1156,19 +1159,19 @@
         <v>29</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D21" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E21">
-        <v>0.78</v>
+        <v>0.73</v>
       </c>
       <c r="F21">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="G21" t="s">
         <v>13</v>
@@ -1177,7 +1180,7 @@
         <v>1.01</v>
       </c>
       <c r="I21" s="1">
-        <v>0.20180000000000001</v>
+        <v>0.21379999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/高波精选组.xlsx
+++ b/高波精选组.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\GopherHK\Fixed Income\结构化产品\HTML 生成\FCN_Watchlist_交接\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66445CB3-693D-4137-8D17-94653BB1EE40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C745A3A-0A57-4B1E-AC5F-75C052D9848D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,6 +52,27 @@
     <t>港股</t>
   </si>
   <si>
+    <t>1138 HK</t>
+  </si>
+  <si>
+    <t>中远海能</t>
+  </si>
+  <si>
+    <t>油气中游</t>
+  </si>
+  <si>
+    <t>欧式敲入</t>
+  </si>
+  <si>
+    <t>6869 HK</t>
+  </si>
+  <si>
+    <t>长飞光纤</t>
+  </si>
+  <si>
+    <t>AI光通信</t>
+  </si>
+  <si>
     <t>1888 HK</t>
   </si>
   <si>
@@ -61,27 +82,6 @@
     <t>电子元件</t>
   </si>
   <si>
-    <t>欧式敲入</t>
-  </si>
-  <si>
-    <t>1138 HK</t>
-  </si>
-  <si>
-    <t>中远海能</t>
-  </si>
-  <si>
-    <t>油气中游</t>
-  </si>
-  <si>
-    <t>6869 HK</t>
-  </si>
-  <si>
-    <t>长飞光纤</t>
-  </si>
-  <si>
-    <t>AI光通信</t>
-  </si>
-  <si>
     <t>992 HK</t>
   </si>
   <si>
@@ -91,6 +91,15 @@
     <t>计算机硬件</t>
   </si>
   <si>
+    <t>3993 HK</t>
+  </si>
+  <si>
+    <t>洛阳钼业</t>
+  </si>
+  <si>
+    <t>工业金属与采矿</t>
+  </si>
+  <si>
     <t>522 HK</t>
   </si>
   <si>
@@ -100,18 +109,18 @@
     <t>半导体设备与材料</t>
   </si>
   <si>
-    <t>3993 HK</t>
-  </si>
-  <si>
-    <t>洛阳钼业</t>
-  </si>
-  <si>
-    <t>工业金属与采矿</t>
-  </si>
-  <si>
     <t>美股</t>
   </si>
   <si>
+    <t>PLTR US</t>
+  </si>
+  <si>
+    <t>帕兰提尔</t>
+  </si>
+  <si>
+    <t>AI软件</t>
+  </si>
+  <si>
     <t>SHOP US</t>
   </si>
   <si>
@@ -121,6 +130,12 @@
     <t>应用软件</t>
   </si>
   <si>
+    <t>DDOG US</t>
+  </si>
+  <si>
+    <t>Datadog</t>
+  </si>
+  <si>
     <t>MRVL US</t>
   </si>
   <si>
@@ -130,12 +145,6 @@
     <t>客制硅/互联</t>
   </si>
   <si>
-    <t>DDOG US</t>
-  </si>
-  <si>
-    <t>Datadog</t>
-  </si>
-  <si>
     <t>NET US</t>
   </si>
   <si>
@@ -145,6 +154,51 @@
     <t>基础软件</t>
   </si>
   <si>
+    <t>BE US</t>
+  </si>
+  <si>
+    <t>Bloom Energy</t>
+  </si>
+  <si>
+    <t>Electrical Equipment &amp; Parts</t>
+  </si>
+  <si>
+    <t>MU US</t>
+  </si>
+  <si>
+    <t>美光</t>
+  </si>
+  <si>
+    <t>内存/HBM</t>
+  </si>
+  <si>
+    <t>DELL US</t>
+  </si>
+  <si>
+    <t>戴尔科技</t>
+  </si>
+  <si>
+    <t>SNDK US</t>
+  </si>
+  <si>
+    <t>闪迪</t>
+  </si>
+  <si>
+    <t>PANW US</t>
+  </si>
+  <si>
+    <t>Palo Alto Networks</t>
+  </si>
+  <si>
+    <t>HPE US</t>
+  </si>
+  <si>
+    <t>慧与科技</t>
+  </si>
+  <si>
+    <t>通信设备</t>
+  </si>
+  <si>
     <t>ALAB US</t>
   </si>
   <si>
@@ -154,51 +208,6 @@
     <t>半导体</t>
   </si>
   <si>
-    <t>TER US</t>
-  </si>
-  <si>
-    <t>泰瑞达</t>
-  </si>
-  <si>
-    <t>HPE US</t>
-  </si>
-  <si>
-    <t>慧与科技</t>
-  </si>
-  <si>
-    <t>通信设备</t>
-  </si>
-  <si>
-    <t>DELL US</t>
-  </si>
-  <si>
-    <t>戴尔科技</t>
-  </si>
-  <si>
-    <t>CRDO US</t>
-  </si>
-  <si>
-    <t>Credo</t>
-  </si>
-  <si>
-    <t>AI互联</t>
-  </si>
-  <si>
-    <t>CIEN US</t>
-  </si>
-  <si>
-    <t>Ciena</t>
-  </si>
-  <si>
-    <t>MU US</t>
-  </si>
-  <si>
-    <t>美光</t>
-  </si>
-  <si>
-    <t>内存/HBM</t>
-  </si>
-  <si>
     <t>FIX US</t>
   </si>
   <si>
@@ -206,15 +215,6 @@
   </si>
   <si>
     <t>工程与建筑</t>
-  </si>
-  <si>
-    <t>HOOD US</t>
-  </si>
-  <si>
-    <t>罗宾汉</t>
-  </si>
-  <si>
-    <t>券商/加密</t>
   </si>
   <si>
     <t>CVNA US</t>
@@ -617,10 +617,10 @@
         <v>12</v>
       </c>
       <c r="E2">
-        <v>0.5</v>
+        <v>0.74</v>
       </c>
       <c r="F2">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="G2" t="s">
         <v>13</v>
@@ -629,7 +629,7 @@
         <v>1.01</v>
       </c>
       <c r="I2" s="1">
-        <v>9.1200000000000003E-2</v>
+        <v>0.18479999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.15">
@@ -646,10 +646,10 @@
         <v>16</v>
       </c>
       <c r="E3">
-        <v>0.74</v>
+        <v>0.62</v>
       </c>
       <c r="F3">
-        <v>0.64</v>
+        <v>0.52</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
@@ -658,7 +658,7 @@
         <v>1.01</v>
       </c>
       <c r="I3" s="1">
-        <v>0.217</v>
+        <v>0.29220000000000002</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.15">
@@ -675,10 +675,10 @@
         <v>19</v>
       </c>
       <c r="E4">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="F4">
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
       <c r="G4" t="s">
         <v>13</v>
@@ -687,7 +687,7 @@
         <v>1.01</v>
       </c>
       <c r="I4" s="1">
-        <v>0.2979</v>
+        <v>0.1105</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.15">
@@ -704,10 +704,10 @@
         <v>22</v>
       </c>
       <c r="E5">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="F5">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="G5" t="s">
         <v>13</v>
@@ -716,7 +716,7 @@
         <v>1.01</v>
       </c>
       <c r="I5" s="1">
-        <v>0.21299999999999999</v>
+        <v>0.23200000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.15">
@@ -733,10 +733,10 @@
         <v>25</v>
       </c>
       <c r="E6">
-        <v>0.73</v>
+        <v>0.84</v>
       </c>
       <c r="F6">
-        <v>0.63</v>
+        <v>0.74</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -745,7 +745,7 @@
         <v>1.01</v>
       </c>
       <c r="I6" s="1">
-        <v>0.1399</v>
+        <v>0.19159999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.15">
@@ -762,10 +762,10 @@
         <v>28</v>
       </c>
       <c r="E7">
-        <v>0.81</v>
+        <v>0.73</v>
       </c>
       <c r="F7">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -774,7 +774,7 @@
         <v>1.01</v>
       </c>
       <c r="I7" s="1">
-        <v>0.14330000000000001</v>
+        <v>0.16619999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.15">
@@ -791,10 +791,10 @@
         <v>32</v>
       </c>
       <c r="E8">
-        <v>0.79</v>
+        <v>0.81</v>
       </c>
       <c r="F8">
-        <v>0.69</v>
+        <v>0.71</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -803,7 +803,7 @@
         <v>1.01</v>
       </c>
       <c r="I8" s="1">
-        <v>0.20499999999999999</v>
+        <v>0.21079999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.15">
@@ -820,10 +820,10 @@
         <v>35</v>
       </c>
       <c r="E9">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="F9">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -832,7 +832,7 @@
         <v>1.01</v>
       </c>
       <c r="I9" s="1">
-        <v>0.19739999999999999</v>
+        <v>0.20630000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.15">
@@ -846,13 +846,13 @@
         <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E10">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="F10">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -861,7 +861,7 @@
         <v>1.01</v>
       </c>
       <c r="I10" s="1">
-        <v>0.20449999999999999</v>
+        <v>0.21229999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.15">
@@ -878,10 +878,10 @@
         <v>40</v>
       </c>
       <c r="E11">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="F11">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
@@ -890,7 +890,7 @@
         <v>1.01</v>
       </c>
       <c r="I11" s="1">
-        <v>0.20749999999999999</v>
+        <v>0.19370000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.15">
@@ -907,10 +907,10 @@
         <v>43</v>
       </c>
       <c r="E12">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="F12">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
@@ -919,7 +919,7 @@
         <v>1.01</v>
       </c>
       <c r="I12" s="1">
-        <v>0.2616</v>
+        <v>0.2127</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.15">
@@ -933,7 +933,7 @@
         <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="E13">
         <v>0.73</v>
@@ -948,7 +948,7 @@
         <v>1.01</v>
       </c>
       <c r="I13" s="1">
-        <v>0.20030000000000001</v>
+        <v>0.27029999999999998</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.15">
@@ -956,19 +956,19 @@
         <v>29</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E14">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="F14">
-        <v>0.65</v>
+        <v>0.73</v>
       </c>
       <c r="G14" t="s">
         <v>13</v>
@@ -977,7 +977,7 @@
         <v>1.01</v>
       </c>
       <c r="I14" s="1">
-        <v>0.19620000000000001</v>
+        <v>0.2036</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.15">
@@ -985,19 +985,19 @@
         <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
         <v>22</v>
       </c>
       <c r="E15">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="F15">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="G15" t="s">
         <v>13</v>
@@ -1006,7 +1006,7 @@
         <v>1.01</v>
       </c>
       <c r="I15" s="1">
-        <v>0.2001</v>
+        <v>0.20169999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.15">
@@ -1014,19 +1014,19 @@
         <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="E16">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="F16">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
@@ -1035,7 +1035,7 @@
         <v>1.01</v>
       </c>
       <c r="I16" s="1">
-        <v>0.27529999999999999</v>
+        <v>0.21240000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.15">
@@ -1049,13 +1049,13 @@
         <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E17">
-        <v>0.71</v>
+        <v>0.79</v>
       </c>
       <c r="F17">
-        <v>0.61</v>
+        <v>0.69</v>
       </c>
       <c r="G17" t="s">
         <v>13</v>
@@ -1064,7 +1064,7 @@
         <v>1.01</v>
       </c>
       <c r="I17" s="1">
-        <v>0.19139999999999999</v>
+        <v>0.19719999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.15">
@@ -1081,10 +1081,10 @@
         <v>58</v>
       </c>
       <c r="E18">
-        <v>0.79</v>
+        <v>0.74</v>
       </c>
       <c r="F18">
-        <v>0.69</v>
+        <v>0.64</v>
       </c>
       <c r="G18" t="s">
         <v>13</v>
@@ -1093,7 +1093,7 @@
         <v>1.01</v>
       </c>
       <c r="I18" s="1">
-        <v>0.15110000000000001</v>
+        <v>0.18990000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.15">
@@ -1110,10 +1110,10 @@
         <v>61</v>
       </c>
       <c r="E19">
-        <v>0.79</v>
+        <v>0.72</v>
       </c>
       <c r="F19">
-        <v>0.69</v>
+        <v>0.62</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
@@ -1122,7 +1122,7 @@
         <v>1.01</v>
       </c>
       <c r="I19" s="1">
-        <v>0.20669999999999999</v>
+        <v>0.26569999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.15">
@@ -1151,7 +1151,7 @@
         <v>1.01</v>
       </c>
       <c r="I20" s="1">
-        <v>0.2026</v>
+        <v>0.1993</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.15">
@@ -1180,7 +1180,7 @@
         <v>1.01</v>
       </c>
       <c r="I21" s="1">
-        <v>0.21379999999999999</v>
+        <v>0.20780000000000001</v>
       </c>
     </row>
   </sheetData>
